--- a/technology_surveys/028_robot_vacuum_product_comparison_survey--technology_surveys.xlsx
+++ b/technology_surveys/028_robot_vacuum_product_comparison_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Robot Vacuum Brand</t>
+          <t>Which robot vacuum brand do you own or have used?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Most Important Feature</t>
+          <t>What feature is most important to you when choosing a robot vacuum?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Second Most Important Feature</t>
+          <t>What feature is second most important to you?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Purchase Satisfaction</t>
+          <t>How satisfied are you with your purchase?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Why You Purchased</t>
+          <t>Why did you purchase your robot vacuum?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,110 +658,110 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>purchase_driver_2</t>
+          <t>price_range</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Purchase Driver 2</t>
+          <t>What is your preferred price range for a robot vacuum?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>purchase_driver_3</t>
+          <t>feature_preference</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Purchase Driver 3</t>
+          <t>What feature would you prefer?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>purchase_driver_4</t>
+          <t>preferred_navigation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Purchase Driver 4</t>
+          <t>What is your preferred navigation system for a robot vacuum?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>purchase_driver_5</t>
+          <t>preferred_model</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Purchase Driver 5</t>
+          <t>What is your preferred model of robot vacuum?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>price_range</t>
+          <t>usage_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Price Range</t>
+          <t>How long have you been using your robot vacuum?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,35 +773,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>feature_preference</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Feature Preference</t>
+          <t>What is your level of satisfaction with your robot vacuum?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>purchase_driver_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Robot Vacuum Model</t>
+          <t>What drives your purchasing decision for a robot vacuum?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>model_2</t>
+          <t>additional_purchasing_driver</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Model 2</t>
+          <t>Additional reasons that drive your purchasing decision for a robot vacuum?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>model_3</t>
+          <t>robot_vacuum_issues</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Model 3</t>
+          <t>Are you experiencing any issues with your current robot vacuum?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,228 +860,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>model_4</t>
+          <t>issues_description</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Model 4</t>
+          <t>Please describe the issues you are experiencing with your current robot vacuum.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>model_5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Model 5</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Purchase Satisfaction 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Purchase Satisfaction 3</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>purchase_driver_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Purchase Driver 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>purchase_driver_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Purchase Driver 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>purchase_driver_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Purchase Driver 4</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>purchase_driver_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Purchase Driver 5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>purchase_driver_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Purchase Driver 6</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>purchase_driver_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Purchase Driver 7</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'irobot'}</t>
+          <t>irobot</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'iRobot'}</t>
+          <t>iRobot</t>
         </is>
       </c>
     </row>
@@ -1148,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'neato'}</t>
+          <t>neato</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Neato'}</t>
+          <t>Neato</t>
         </is>
       </c>
     </row>
@@ -1165,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'samsung'}</t>
+          <t>samsung</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Samsung'}</t>
+          <t>Samsung</t>
         </is>
       </c>
     </row>
@@ -1182,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'suction_power'}</t>
+          <t>suction_power</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Suction Power'}</t>
+          <t>Suction Power</t>
         </is>
       </c>
     </row>
@@ -1199,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'navigation'}</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Navigation'}</t>
+          <t>Navigation</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'charging_time'}</t>
+          <t>charging_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Charging Time'}</t>
+          <t>Charging Time</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1026,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'price'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Price'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>feature_importance_choices</t>
+          <t>feature_importance_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'navigation_system'}</t>
+          <t>suction_power</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Navigation System'}</t>
+          <t>Suction Power</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'suction_power'}</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Suction Power'}</t>
+          <t>Navigation</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'navigation'}</t>
+          <t>charging_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Navigation'}</t>
+          <t>Charging Time</t>
         </is>
       </c>
     </row>
@@ -1301,46 +1094,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'charging_time'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Charging Time'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>feature_importance_2_choices</t>
+          <t>purchase_satisfaction_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'price'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Price'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>feature_importance_2_choices</t>
+          <t>purchase_satisfaction_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'navigation_system'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Navigation System'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1352,46 +1145,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Very Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>purchase_satisfaction_choices</t>
+          <t>purchase_driver_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat Satisfied'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>purchase_satisfaction_choices</t>
+          <t>purchase_driver_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfied'}</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Not Satisfied'}</t>
+          <t>Recommendation</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'price'}</t>
+          <t>product_reviews</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Price'}</t>
+          <t>Product Reviews</t>
         </is>
       </c>
     </row>
@@ -1420,1132 +1213,435 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'recommendation'}</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Recommendation'}</t>
+          <t>Brand</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>purchase_driver_choices</t>
+          <t>price_range_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'product_reviews'}</t>
+          <t>0-500</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Product Reviews'}</t>
+          <t>0-500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>purchase_driver_choices</t>
+          <t>price_range_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'brand'}</t>
+          <t>500-1000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Brand'}</t>
+          <t>500-1000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>purchase_driver_choices</t>
+          <t>price_range_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>1000-2000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>1000-2000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>purchase_driver_2_choices</t>
+          <t>price_range_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>2000-3000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2000-3000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>purchase_driver_2_choices</t>
+          <t>price_range_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>purchase_driver_3_choices</t>
+          <t>feature_preference_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'price'}</t>
+          <t>suction_power</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Price'}</t>
+          <t>Suction Power</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>purchase_driver_3_choices</t>
+          <t>feature_preference_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'recommendation'}</t>
+          <t>navigation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Recommendation'}</t>
+          <t>Navigation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>purchase_driver_3_choices</t>
+          <t>feature_preference_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'product_reviews'}</t>
+          <t>charging_time</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Product Reviews'}</t>
+          <t>Charging Time</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>purchase_driver_3_choices</t>
+          <t>feature_preference_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'brand'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Brand'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>purchase_driver_4_choices</t>
+          <t>feature_preference_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'price'}</t>
+          <t>navigation_system</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Price'}</t>
+          <t>Navigation System</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>purchase_driver_4_choices</t>
+          <t>preferred_navigation_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'recommendation'}</t>
+          <t>laser_navigation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Recommendation'}</t>
+          <t>Laser Navigation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>purchase_driver_4_choices</t>
+          <t>preferred_navigation_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'product_reviews'}</t>
+          <t>camera_navigation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Product Reviews'}</t>
+          <t>Camera Navigation</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>purchase_driver_4_choices</t>
+          <t>preferred_navigation_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'brand'}</t>
+          <t>sensor_navigation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Brand'}</t>
+          <t>Sensor Navigation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>purchase_driver_5_choices</t>
+          <t>preferred_navigation_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>purchase_driver_5_choices</t>
+          <t>preferred_model_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>irobot</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>iRobot</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>preferred_model_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'0-500'}</t>
+          <t>neato</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': '0-500'}</t>
+          <t>Neato</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>preferred_model_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'500-1000'}</t>
+          <t>samsung</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': '500-1000'}</t>
+          <t>Samsung</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>preferred_model_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'1000-2000'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': '1000-2000'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'2000-3000'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': '2000-3000'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>feature_preference_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'suction_power'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Suction Power'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>feature_preference_choices</t>
+          <t>purchase_driver_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'navigation'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Navigation'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>feature_preference_choices</t>
+          <t>purchase_driver_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'charging_time'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Charging Time'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>feature_preference_choices</t>
+          <t>robot_vacuum_issues_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'price'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Price'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>feature_preference_choices</t>
+          <t>robot_vacuum_issues_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'navigation_system'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>{'value': 'Navigation System'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>model_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'value':_'irobot'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'value': 'iRobot'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>model_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'value':_'neato'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'value': 'Neato'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>model_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'value':_'samsung'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'value': 'Samsung'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>model_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'value':_'irobot'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'value': 'iRobot'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>model_2_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'value':_'neato'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'value': 'Neato'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>model_2_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'value':_'samsung'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'value': 'Samsung'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>model_3_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>model_3_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>model_4_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'value':_'irobot'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'value': 'iRobot'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>model_4_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'value':_'neato'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'value': 'Neato'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>model_4_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'value':_'samsung'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'value': 'Samsung'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>model_5_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>model_5_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>{'value':_'very_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>{'value': 'Very Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>{'value':_'not_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>{'value': 'Not Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>{'value':_'very_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>{'value': 'Very Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>purchase_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>{'value':_'not_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>{'value': 'Not Satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>purchase_driver_2_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>{'value':_'price'}</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>{'value': 'Price'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>purchase_driver_2_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>{'value':_'recommendation'}</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>{'value': 'Recommendation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>purchase_driver_2_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>{'value':_'product_reviews'}</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>{'value': 'Product Reviews'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>purchase_driver_2_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>{'value':_'brand'}</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>{'value': 'Brand'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>purchase_driver_3_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>{'value':_'price'}</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>{'value': 'Price'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>purchase_driver_3_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>{'value':_'recommendation'}</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>{'value': 'Recommendation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>purchase_driver_3_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>{'value':_'product_reviews'}</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>{'value': 'Product Reviews'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>purchase_driver_3_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>{'value':_'brand'}</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>{'value': 'Brand'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>purchase_driver_4_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>{'value':_'price'}</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>{'value': 'Price'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>purchase_driver_4_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>{'value':_'recommendation'}</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>{'value': 'Recommendation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>purchase_driver_4_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>{'value':_'product_reviews'}</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>{'value': 'Product Reviews'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>purchase_driver_4_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>{'value':_'brand'}</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>{'value': 'Brand'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>purchase_driver_5_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>{'value':_'price'}</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>{'value': 'Price'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>purchase_driver_5_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>{'value':_'recommendation'}</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>{'value': 'Recommendation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>purchase_driver_5_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>{'value':_'product_reviews'}</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>{'value': 'Product Reviews'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>purchase_driver_5_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>{'value':_'brand'}</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>{'value': 'Brand'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>purchase_driver_6_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>{'value':_'price'}</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>{'value': 'Price'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>purchase_driver_6_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>{'value':_'recommendation'}</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>{'value': 'Recommendation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>purchase_driver_6_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>{'value':_'product_reviews'}</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>{'value': 'Product Reviews'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>purchase_driver_6_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>{'value':_'brand'}</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>{'value': 'Brand'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>purchase_driver_7_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>purchase_driver_7_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
         <is>
           <t>No</t>
         </is>
